--- a/education_forms/021_educational_impact_story_sharing_consent_form--education_forms.xlsx
+++ b/education_forms/021_educational_impact_story_sharing_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,8 +880,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -909,12 +909,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'attribution'}</t>
+          <t>attribution</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Attribution'}</t>
+          <t>Attribution</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'anonymous'}</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Anonymous'}</t>
+          <t>Anonymous</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'publicly'}</t>
+          <t>publicly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Publicly'}</t>
+          <t>Publicly</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'privately'}</t>
+          <t>privately</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Privately'}</t>
+          <t>Privately</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'with_educators'}</t>
+          <t>with_educators</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'With educators'}</t>
+          <t>With educators</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'with_the_school_community'}</t>
+          <t>with_the_school_community</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'With the school community'}</t>
+          <t>With the school community</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
